--- a/data/trans_orig/P6902-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6902-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24003</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18947</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55328</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>70239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72646</t>
+          <t>72652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91806</t>
+          <t>90743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50472</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75023</t>
+          <t>75509</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31611</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73130</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102390</t>
+          <t>102304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70958</t>
+          <t>70472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95509</t>
+          <t>95097</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>35694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96387</t>
+          <t>96473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125647</t>
+          <t>125831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>36584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58458</t>
+          <t>58302</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>36663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64995</t>
+          <t>64418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92319</t>
+          <t>90022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>51642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74380</t>
+          <t>73360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>22757</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64158</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91482</t>
+          <t>92059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66676</t>
+          <t>67173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90365</t>
+          <t>89251</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35878</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>108283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138333</t>
+          <t>139823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46684</t>
+          <t>47798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70373</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>33492</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52673</t>
+          <t>52693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87267</t>
+          <t>85777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116986</t>
+          <t>117317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182842</t>
+          <t>185412</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>226766</t>
+          <t>229307</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129325</t>
+          <t>126680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>292085</t>
+          <t>292908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>345489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245539</t>
+          <t>242998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289463</t>
+          <t>286893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>93441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>122453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348448</t>
+          <t>346938</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400342</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36201</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25088</t>
+          <t>24695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36820</t>
+          <t>35435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57352</t>
+          <t>57687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40379</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56488</t>
+          <t>56836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54482</t>
+          <t>54147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75014</t>
+          <t>76399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55781</t>
+          <t>55512</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29000</t>
+          <t>27493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>70292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>36053</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54561</t>
+          <t>55224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34498</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58868</t>
+          <t>59302</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85037</t>
+          <t>84771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>32084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>52053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21193</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58031</t>
+          <t>56254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80967</t>
+          <t>81693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48301</t>
+          <t>47473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31786</t>
+          <t>31442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51569</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74505</t>
+          <t>76282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28554</t>
+          <t>28288</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45853</t>
+          <t>45332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>64873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88347</t>
+          <t>89614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>32070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48848</t>
+          <t>49114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53152</t>
+          <t>51885</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77828</t>
+          <t>76626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133156</t>
+          <t>134651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170842</t>
+          <t>170371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108010</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138217</t>
+          <t>138490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252559</t>
+          <t>251828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300396</t>
+          <t>299706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,41%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154263</t>
+          <t>154734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191949</t>
+          <t>190454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>77338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240537</t>
+          <t>241227</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288374</t>
+          <t>289105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,45%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>30908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46666</t>
+          <t>46492</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23570</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38601</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21174</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57263</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,48%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31435</t>
+          <t>32161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52595</t>
+          <t>52714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37082</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57982</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82931</t>
+          <t>84439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44389</t>
+          <t>44270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65549</t>
+          <t>64823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18470</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33617</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69604</t>
+          <t>68096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94553</t>
+          <t>94643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47439</t>
+          <t>47023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33188</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49314</t>
+          <t>49516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65590</t>
+          <t>64684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91675</t>
+          <t>91272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62496</t>
+          <t>62912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83016</t>
+          <t>83241</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83007</t>
+          <t>83410</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109092</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41752</t>
+          <t>41472</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60133</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53031</t>
+          <t>52410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84039</t>
+          <t>83938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107932</t>
+          <t>107273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>28150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46658</t>
+          <t>46938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>29932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70454</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132290</t>
+          <t>132941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170699</t>
+          <t>171739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145027</t>
+          <t>144767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>256966</t>
+          <t>258995</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307060</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,37%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179302</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>217711</t>
+          <t>217060</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71271</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100351</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259239</t>
+          <t>258428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309333</t>
+          <t>307304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40726</t>
+          <t>40788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51521</t>
+          <t>52715</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74990</t>
+          <t>75066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16583</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28828</t>
+          <t>27678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>50831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74376</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,13%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48823</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71311</t>
+          <t>71561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54692</t>
+          <t>54660</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70715</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108905</t>
+          <t>108539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137702</t>
+          <t>136881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40672</t>
+          <t>40422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63160</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>44070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73010</t>
+          <t>73831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101807</t>
+          <t>102173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28466</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43274</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18942</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72822</t>
+          <t>72813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39182</t>
+          <t>43053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110232</t>
+          <t>109154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26811</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24086</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>78701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41952</t>
+          <t>43030</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113002</t>
+          <t>109131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72363</t>
+          <t>71844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88491</t>
+          <t>87701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59649</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81491</t>
+          <t>81070</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137864</t>
+          <t>139071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>166274</t>
+          <t>165682</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22826</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>45341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67062</t>
+          <t>65855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,14%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191466</t>
+          <t>190398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227618</t>
+          <t>227815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149821</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243927</t>
+          <t>241655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354902</t>
+          <t>349388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>460070</t>
+          <t>456275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,77%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111887</t>
+          <t>111690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148039</t>
+          <t>149107</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>110288</t>
+          <t>112560</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204394</t>
+          <t>202758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>233650</t>
+          <t>237445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338818</t>
+          <t>344332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
